--- a/models/7974_DCF_Model_20260906.xlsx
+++ b/models/7974_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F0DA96-06FE-4716-8D00-1F4FA7B22E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5DEC1A-88BF-479A-84CA-C41E4F8E9A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="349">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -789,7 +789,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 19:25, template rev 63983ab</t>
+    <t>Generated by pipeline on 2026-09-06 23:19, template rev 041abe3</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -822,6 +822,12 @@
     <t>value</t>
   </si>
   <si>
+    <t>annual_doc_ids</t>
+  </si>
+  <si>
+    <t>2026-03-31=S100Y9NX, 2025-03-31=S100W73A, 2024-03-31=S100TMMG, 2023-03-31=S100QY8A, 2022-03-31=S100O9PP</t>
+  </si>
+  <si>
     <t>auto_log_entries</t>
   </si>
   <si>
@@ -966,6 +972,12 @@
     <t>0.01024</t>
   </si>
   <si>
+    <t>disclosure_basis_date</t>
+  </si>
+  <si>
+    <t>2026-03-31</t>
+  </si>
+  <si>
     <t>fs_year_coverage</t>
   </si>
   <si>
@@ -993,7 +1005,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 19:25:57</t>
+    <t>2026-09-06 23:19:50</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1065,7 +1077,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>63983ab</t>
+    <t>041abe3</t>
   </si>
   <si>
     <t>ticker</t>
@@ -6391,7 +6403,7 @@
   <sheetPr>
     <tabColor rgb="FF808080"/>
   </sheetPr>
-  <dimension ref="B2:G60"/>
+  <dimension ref="B2:G62"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -6509,15 +6521,15 @@
         <v>268</v>
       </c>
       <c r="C17" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C18" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6549,31 +6561,31 @@
         <v>277</v>
       </c>
       <c r="C22" t="s">
-        <v>44</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C23" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C24" t="s">
-        <v>249</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C25" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6581,23 +6593,23 @@
         <v>282</v>
       </c>
       <c r="C26" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C27" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C28" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6621,31 +6633,31 @@
         <v>290</v>
       </c>
       <c r="C31" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C32" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
     </row>
     <row r="33" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C33" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
     </row>
     <row r="34" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C34" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
     </row>
     <row r="35" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6693,15 +6705,15 @@
         <v>305</v>
       </c>
       <c r="C40" t="s">
-        <v>274</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C41" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
     </row>
     <row r="42" spans="2:3" ht="14" x14ac:dyDescent="0.3">
@@ -6853,6 +6865,22 @@
         <v>344</v>
       </c>
       <c r="C60" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="61" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B61" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C61" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" ht="14" x14ac:dyDescent="0.3">
+      <c r="B62" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C62" t="s">
         <v>209</v>
       </c>
     </row>
